--- a/output/pdf_financials_xlsx/JPWR.H.xlsx
+++ b/output/pdf_financials_xlsx/JPWR.H.xlsx
@@ -2139,22 +2139,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.245566</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.711071</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.240703</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.240703</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.129524</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.277111</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>2.917885</v>
@@ -2225,22 +2225,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.245566</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.711071</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.240703</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.240703</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.129524</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.277111</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>2.917885</v>
@@ -2741,22 +2741,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.421087</v>
+        <v>0.175521</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.11097</v>
+        <v>0.399899</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.201037</v>
+        <v>1.960334</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.201037</v>
+        <v>1.960334</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>6.434495</v>
+        <v>5.304971</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>5.642033</v>
+        <v>4.364922</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>4.941258</v>
@@ -18756,7 +18756,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -20352,7 +20352,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -22492,7 +22492,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E211" s="5" t="n">

--- a/output/pdf_financials_xlsx/JPWR.H.xlsx
+++ b/output/pdf_financials_xlsx/JPWR.H.xlsx
@@ -1183,7 +1183,7 @@
         <v>-33.555651</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>3.234214</v>
+        <v>8.629694000000001</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>4.192837</v>
@@ -1236,7 +1236,7 @@
         <v>-1.056681</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>-5.39548</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>0.033441</v>
@@ -1826,7 +1826,7 @@
         <v>-33.555651</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.234214</v>
+        <v>8.629694000000001</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>4.192837</v>
@@ -1932,7 +1932,7 @@
         <v>-29.684397</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>8.832722</v>
+        <v>14.228202</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>0.959923</v>
@@ -1985,7 +1985,7 @@
         <v>-242.4725745572366</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>50.94832743714637</v>
+        <v>82.07018112172678</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>5.429902313878281</v>
@@ -2038,7 +2038,7 @@
         <v>-3.149040380709646</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>62.52226324595055</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>0.7975745300854767</v>
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.127268</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.243552</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>0</v>
@@ -5418,16 +5418,16 @@
         <v>0</v>
       </c>
       <c r="C108" s="3" t="n">
-        <v>0</v>
+        <v>3.269905</v>
       </c>
       <c r="D108" s="3" t="n">
-        <v>0</v>
+        <v>15.39</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>0</v>
+        <v>16.952029</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>0</v>
+        <v>6.984037</v>
       </c>
       <c r="G108" s="1" t="inlineStr">
         <is>
@@ -5505,16 +5505,16 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.053034</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.178714</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.788528</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>2.696844</v>
       </c>
       <c r="F110" s="3" t="n">
         <v>0</v>
@@ -27944,7 +27944,11 @@
           <t>Proceeds from units issued pursuant to a Private Placement (note 8 (i))</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -28598,7 +28602,11 @@
           <t>Deferred Income tax (recovery) (note 7)</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr"/>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E293" t="inlineStr">
         <is>
           <t>-</t>
@@ -32632,7 +32640,11 @@
           <t>Deferred income tax expense (note 17)</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr"/>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E347" t="inlineStr">
         <is>
           <t>-</t>
@@ -34442,7 +34454,11 @@
           <t>Impairment charges (Note 6, 7)</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr"/>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E371" t="inlineStr">
         <is>
           <t>-</t>
@@ -34516,7 +34532,11 @@
           <t>Deferred income tax recovery (Note 16)</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr"/>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E372" t="inlineStr">
         <is>
           <t>-</t>
@@ -35416,7 +35436,11 @@
           <t>Receipt in advance of private placement (Note 11)</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr"/>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr">
         <is>
           <t>-</t>
@@ -36468,7 +36492,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D398" t="inlineStr"/>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E398" s="5" t="n">
         <v>0.053034</v>
       </c>
@@ -36616,7 +36644,11 @@
           <t>Impairment charge</t>
         </is>
       </c>
-      <c r="D400" t="inlineStr"/>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E400" t="inlineStr">
         <is>
           <t>-</t>
@@ -36688,7 +36720,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D401" t="inlineStr"/>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E401" t="inlineStr">
         <is>
           <t>-</t>
@@ -37798,7 +37834,11 @@
           <t>Receipt in advance of private placement</t>
         </is>
       </c>
-      <c r="D416" t="inlineStr"/>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E416" t="inlineStr">
         <is>
           <t>-</t>
@@ -39140,7 +39180,11 @@
           <t>Impairment charge (Note 6)</t>
         </is>
       </c>
-      <c r="D434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E434" t="inlineStr">
         <is>
           <t>-</t>
@@ -39290,7 +39334,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E436" s="5" t="n">
         <v>0.002961</v>
       </c>
@@ -46698,7 +46746,11 @@
           <t>Deferred income tax recovery (Note 16)</t>
         </is>
       </c>
-      <c r="D535" t="inlineStr"/>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E535" t="inlineStr">
         <is>
           <t>-</t>
